--- a/Random Forest Sample Code/Experiment Parameter Data.xlsx
+++ b/Random Forest Sample Code/Experiment Parameter Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clim/Developer/GitHub/CRLM-Experiments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clim/Developer/GitHub/CRLM-Experiments/Random Forest Sample Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6C239FF-E98A-A749-83FC-A1DA2C303CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01895DEA-8BCF-2A4F-B74F-13B4FCB81393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23380" yWindow="500" windowWidth="15020" windowHeight="21100" xr2:uid="{F425073B-028D-0647-BE39-C23F1B537A29}"/>
+    <workbookView xWindow="4500" yWindow="8040" windowWidth="29400" windowHeight="18380" xr2:uid="{F425073B-028D-0647-BE39-C23F1B537A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t># of patients = 24, # of lesions = 113 (65 malignant, 48 benign)</t>
   </si>
@@ -84,6 +84,30 @@
   </si>
   <si>
     <t>2024-09-15_20.12.49</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>FNR</t>
+  </si>
+  <si>
+    <t>FPR</t>
+  </si>
+  <si>
+    <t>Classification Rate</t>
+  </si>
+  <si>
+    <t>2024-11-17_21.58.00</t>
+  </si>
+  <si>
+    <t>2024-11-18_08.41.09</t>
+  </si>
+  <si>
+    <t>2024-11-18 13.28.59</t>
+  </si>
+  <si>
+    <t>[10, 200]</t>
   </si>
 </sst>
 </file>
@@ -470,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9098437E-B678-1446-9AB2-E7EFAFEA46AD}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -480,21 +504,33 @@
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -514,7 +550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -534,7 +570,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -554,7 +590,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -574,7 +610,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -591,7 +627,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -609,6 +645,102 @@
       </c>
       <c r="F8">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>0.70784000000000002</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>0.8</v>
+      </c>
+      <c r="G9">
+        <v>0.53100999999999998</v>
+      </c>
+      <c r="H9">
+        <v>0.27722000000000002</v>
+      </c>
+      <c r="I9">
+        <v>0.33067999999999997</v>
+      </c>
+      <c r="J9">
+        <v>0.30103999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>0.70784000000000002</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <v>0.8</v>
+      </c>
+      <c r="G10">
+        <v>0.53100999999999998</v>
+      </c>
+      <c r="H10">
+        <v>0.27722000000000002</v>
+      </c>
+      <c r="I10">
+        <v>0.33067999999999997</v>
+      </c>
+      <c r="J10">
+        <v>0.30103999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>0.70769000000000004</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>0.8</v>
+      </c>
+      <c r="G11">
+        <v>0.54915000000000003</v>
+      </c>
+      <c r="H11">
+        <v>0.28814000000000001</v>
+      </c>
+      <c r="I11">
+        <v>0.30120000000000002</v>
+      </c>
+      <c r="J11">
+        <v>0.30098000000000003</v>
       </c>
     </row>
   </sheetData>
